--- a/outputs/ToT_percentile_classification_matrix.xlsx
+++ b/outputs/ToT_percentile_classification_matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3840" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3840" uniqueCount="217">
   <si>
     <t>2013 Jan</t>
   </si>
@@ -572,6 +572,9 @@
   </si>
   <si>
     <t>Alarm</t>
+  </si>
+  <si>
+    <t>No data</t>
   </si>
   <si>
     <t>20%</t>
@@ -1999,13 +2002,13 @@
         <v>183</v>
       </c>
       <c r="FB2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="FC2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="FD2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="3" spans="1:160">
@@ -2481,13 +2484,13 @@
         <v>183</v>
       </c>
       <c r="FB3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="FC3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="FD3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="4" spans="1:160">
@@ -2780,7 +2783,7 @@
         <v>183</v>
       </c>
       <c r="CS4" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="CT4" t="s">
         <v>183</v>
@@ -2963,13 +2966,13 @@
         <v>183</v>
       </c>
       <c r="FB4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="FC4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="FD4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="5" spans="1:160">
@@ -3445,13 +3448,13 @@
         <v>183</v>
       </c>
       <c r="FB5" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="FC5" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="FD5" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="6" spans="1:160">
@@ -3927,13 +3930,13 @@
         <v>183</v>
       </c>
       <c r="FB6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="FC6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="FD6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="7" spans="1:160">
@@ -4409,13 +4412,13 @@
         <v>183</v>
       </c>
       <c r="FB7" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="FC7" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="FD7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="8" spans="1:160">
@@ -4891,13 +4894,13 @@
         <v>185</v>
       </c>
       <c r="FB8" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="FC8" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="FD8" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="9" spans="1:160">
@@ -5373,13 +5376,13 @@
         <v>183</v>
       </c>
       <c r="FB9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="FC9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="FD9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="10" spans="1:160">
@@ -5855,13 +5858,13 @@
         <v>183</v>
       </c>
       <c r="FB10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="FC10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="FD10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11" spans="1:160">
@@ -6337,13 +6340,13 @@
         <v>183</v>
       </c>
       <c r="FB11" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="FC11" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="FD11" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="12" spans="1:160">
@@ -6819,13 +6822,13 @@
         <v>183</v>
       </c>
       <c r="FB12" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="FC12" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="FD12" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="13" spans="1:160">
@@ -7241,7 +7244,7 @@
         <v>183</v>
       </c>
       <c r="EH13" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="EI13" t="s">
         <v>183</v>
@@ -7301,13 +7304,13 @@
         <v>184</v>
       </c>
       <c r="FB13" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="FC13" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="FD13" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="14" spans="1:160">
@@ -7783,13 +7786,13 @@
         <v>183</v>
       </c>
       <c r="FB14" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="FC14" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="FD14" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="15" spans="1:160">
@@ -8265,13 +8268,13 @@
         <v>183</v>
       </c>
       <c r="FB15" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="FC15" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="FD15" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="16" spans="1:160">
@@ -8747,13 +8750,13 @@
         <v>183</v>
       </c>
       <c r="FB16" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="FC16" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="FD16" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="17" spans="1:160">
@@ -8980,217 +8983,217 @@
         <v>183</v>
       </c>
       <c r="BW17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="BX17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="BY17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="BZ17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="CA17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="CB17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="CC17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="CD17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="CE17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="CF17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="CG17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="CH17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="CI17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="CJ17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="CK17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="CL17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="CM17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="CN17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="CO17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="CP17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="CQ17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="CR17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="CS17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="CT17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="CU17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="CV17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="CW17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="CX17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="CY17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="CZ17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="DA17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="DB17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="DC17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="DD17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="DE17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="DF17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="DG17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="DH17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="DI17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="DJ17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="DK17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="DL17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="DM17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="DN17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="DO17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="DP17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="DQ17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="DR17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="DS17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="DT17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="DU17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="DV17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="DW17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="DX17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="DY17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="DZ17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="EA17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="EB17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="EC17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="ED17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="EE17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="EF17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="EG17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="EH17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="EI17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="EJ17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="EK17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="EL17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="EM17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="EN17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="EO17" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="EP17" t="s">
         <v>183</v>
@@ -9229,13 +9232,13 @@
         <v>183</v>
       </c>
       <c r="FB17" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="FC17" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="FD17" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="18" spans="1:160">
@@ -9711,13 +9714,13 @@
         <v>183</v>
       </c>
       <c r="FB18" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="FC18" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="FD18" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="19" spans="1:160">
@@ -10193,13 +10196,13 @@
         <v>183</v>
       </c>
       <c r="FB19" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="FC19" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="FD19" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="20" spans="1:160">
@@ -10675,13 +10678,13 @@
         <v>183</v>
       </c>
       <c r="FB20" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="FC20" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="FD20" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="21" spans="1:160">
@@ -11157,13 +11160,13 @@
         <v>183</v>
       </c>
       <c r="FB21" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="FC21" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="FD21" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="22" spans="1:160">
@@ -11639,13 +11642,13 @@
         <v>183</v>
       </c>
       <c r="FB22" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="FC22" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="FD22" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="23" spans="1:160">
@@ -12010,7 +12013,7 @@
         <v>185</v>
       </c>
       <c r="DQ23" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="DR23" t="s">
         <v>185</v>
@@ -12121,13 +12124,13 @@
         <v>184</v>
       </c>
       <c r="FB23" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="FC23" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="FD23" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="24" spans="1:160">
@@ -12603,13 +12606,13 @@
         <v>183</v>
       </c>
       <c r="FB24" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="FC24" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="FD24" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/ToT_percentile_classification_matrix.xlsx
+++ b/outputs/ToT_percentile_classification_matrix.xlsx
@@ -565,7 +565,7 @@
     <t>West Pokot</t>
   </si>
   <si>
-    <t>Minimal</t>
+    <t>No concern</t>
   </si>
   <si>
     <t>No data</t>
